--- a/data/up1_2_3_4_visc_sem.xlsx
+++ b/data/up1_2_3_4_visc_sem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arkema-my.sharepoint.com/personal/a6131250_arkema_com/Documents/finish_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942968FD-E942-4A03-B0F2-4A39AE5AC748}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-15040" windowWidth="38620" windowHeight="21100" xr2:uid="{C900D49F-5873-4F17-88DC-CFF44F40CE34}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>time</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>filename w/ k -&gt; &lt;magnification&gt; * 1000</t>
+  </si>
+  <si>
+    <t>up3_rho</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -287,7 +293,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -300,9 +306,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -660,6 +664,7 @@
     <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -715,8 +720,11 @@
       <c r="A12" t="s">
         <v>0</v>
       </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -740,7 +748,7 @@
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
         <v>14</v>
@@ -814,8 +822,11 @@
         <v>44897.684027777781</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="D13" t="s">
+      <c r="C13" t="s">
         <v>28</v>
+      </c>
+      <c r="D13">
+        <v>16.439521245304078</v>
       </c>
       <c r="E13">
         <v>25</v>
@@ -842,7 +853,8 @@
         <v>40.699999999999996</v>
       </c>
       <c r="L13">
-        <v>16.439521245304078</v>
+        <f>1000*1.11730058759368</f>
+        <v>1117.3005875936799</v>
       </c>
       <c r="M13" s="9">
         <v>54.862543083327509</v>
@@ -916,8 +928,11 @@
         <v>44902.488194444442</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="D14" t="s">
+      <c r="C14" t="s">
         <v>29</v>
+      </c>
+      <c r="D14">
+        <v>18.120530314065213</v>
       </c>
       <c r="E14">
         <v>25</v>
@@ -940,11 +955,11 @@
         <f t="shared" si="2"/>
         <v>37.479999999999997</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <v>42.67</v>
       </c>
-      <c r="L14">
-        <v>18.120530314065213</v>
+      <c r="L14" t="s">
+        <v>55</v>
       </c>
       <c r="M14" s="9">
         <v>69.187853905185278</v>
@@ -1018,8 +1033,11 @@
         <v>44902.617361111108</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="D15" t="s">
+      <c r="C15" t="s">
         <v>30</v>
+      </c>
+      <c r="D15">
+        <v>18.108556658942508</v>
       </c>
       <c r="E15">
         <v>25</v>
@@ -1042,11 +1060,11 @@
         <f t="shared" si="2"/>
         <v>33.159999999999997</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15">
         <v>40.61</v>
       </c>
-      <c r="L15">
-        <v>18.108556658942508</v>
+      <c r="L15" t="s">
+        <v>55</v>
       </c>
       <c r="M15" s="9">
         <v>69.783755549506239</v>
@@ -1084,34 +1102,34 @@
       <c r="X15">
         <v>42.446493159999214</v>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y15" s="3">
         <v>5.48</v>
       </c>
-      <c r="Z15" s="12">
+      <c r="Z15" s="3">
         <v>6.54</v>
       </c>
-      <c r="AA15" s="12">
+      <c r="AA15" s="3">
         <v>7.4</v>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB15" s="3">
         <v>8.2100000000000009</v>
       </c>
-      <c r="AC15" s="12">
+      <c r="AC15" s="3">
         <v>9.07</v>
       </c>
-      <c r="AD15" s="12">
+      <c r="AD15" s="3">
         <v>10.039999999999999</v>
       </c>
-      <c r="AE15" s="12">
+      <c r="AE15" s="3">
         <v>11.24</v>
       </c>
-      <c r="AF15" s="12">
+      <c r="AF15" s="3">
         <v>12.95</v>
       </c>
-      <c r="AG15" s="12">
+      <c r="AG15" s="3">
         <v>16.2</v>
       </c>
-      <c r="AH15" s="12">
+      <c r="AH15" s="3">
         <v>34.119999999999997</v>
       </c>
     </row>
@@ -1120,8 +1138,11 @@
         <v>44902.736111111109</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="D16" t="s">
+      <c r="C16" t="s">
         <v>31</v>
+      </c>
+      <c r="D16">
+        <v>19.279125684726509</v>
       </c>
       <c r="E16">
         <v>25</v>
@@ -1144,11 +1165,11 @@
         <f t="shared" si="2"/>
         <v>33.159999999999997</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <v>38.769999999999996</v>
       </c>
-      <c r="L16">
-        <v>19.279125684726509</v>
+      <c r="L16" t="s">
+        <v>55</v>
       </c>
       <c r="M16" s="9">
         <v>72.697462817981162</v>
@@ -1186,38 +1207,38 @@
       <c r="X16">
         <v>56.105365272337373</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="3">
         <v>5.39</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="3">
         <v>6.37</v>
       </c>
-      <c r="AA16" s="12">
+      <c r="AA16" s="3">
         <v>7.15</v>
       </c>
-      <c r="AB16" s="12">
+      <c r="AB16" s="3">
         <v>7.9</v>
       </c>
-      <c r="AC16" s="12">
+      <c r="AC16" s="3">
         <v>8.67</v>
       </c>
-      <c r="AD16" s="12">
+      <c r="AD16" s="3">
         <v>9.5299999999999994</v>
       </c>
-      <c r="AE16" s="12">
+      <c r="AE16" s="3">
         <v>10.59</v>
       </c>
-      <c r="AF16" s="12">
+      <c r="AF16" s="3">
         <v>12.11</v>
       </c>
-      <c r="AG16" s="12">
+      <c r="AG16" s="3">
         <v>14.9</v>
       </c>
-      <c r="AH16" s="12">
+      <c r="AH16" s="3">
         <v>29.26</v>
       </c>
     </row>
-    <row r="17" spans="21:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="32:41" x14ac:dyDescent="0.25">
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
@@ -1229,18 +1250,7 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
     </row>
-    <row r="18" spans="21:41" x14ac:dyDescent="0.25">
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
+    <row r="18" spans="32:41" x14ac:dyDescent="0.25">
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
@@ -1344,36 +1354,36 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1728,376 +1738,376 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>15.000299999999999</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>638.48500000000001</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>203.245</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>0.31832300000000002</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>24.76</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <v>30.000299999999999</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>448.197</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>226.13</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>0.50453199999999998</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <v>24.83</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <v>45.000300000000003</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>316.94499999999999</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>253.44800000000001</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>0.79965900000000001</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>24.91</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <v>60.000300000000003</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>226.59700000000001</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <v>287.17099999999999</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>1.26732</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>24.97</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="14">
+      <c r="B10" s="12">
         <v>75.000299999999996</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <v>156.52699999999999</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <v>314.387</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>2.0085199999999999</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>25.05</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="14">
+      <c r="B11" s="12">
         <v>90.000299999999996</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="12">
         <v>80.064400000000006</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <v>254.88800000000001</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>3.1835399999999998</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <v>25.08</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <v>105</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="12">
         <v>43.174700000000001</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <v>217.822</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>5.04514</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>25.13</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <v>120</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <v>29.406600000000001</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <v>235.14</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>7.9961599999999997</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>25.15</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <v>135</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="12">
         <v>18.837900000000001</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="12">
         <v>238.721</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>12.6724</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>25.16</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="14">
+      <c r="B15" s="12">
         <v>150</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="12">
         <v>12.2933</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <v>246.90199999999999</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>20.084399999999999</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <v>25.17</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="14">
+      <c r="B16" s="12">
         <v>165</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="12">
         <v>8.2373600000000007</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="12">
         <v>262.20400000000001</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>31.831099999999999</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>25.16</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <v>180</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="12">
         <v>5.4910600000000001</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <v>277.03100000000001</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <v>50.4512</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <v>25.15</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <v>195</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>3.7642699999999998</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>300.98899999999998</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>79.959500000000006</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>25.13</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="14">
+      <c r="B19" s="12">
         <v>210</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>2.58968</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <v>328.19200000000001</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>126.73099999999999</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>25.11</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="14">
+      <c r="B20" s="12">
         <v>225</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>1.5803199999999999</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <v>317.37900000000002</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>200.83199999999999</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>25.09</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="14">
+      <c r="B21" s="12">
         <v>240</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <v>0.84790200000000004</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <v>269.91199999999998</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>318.32900000000001</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>25.05</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="14">
+      <c r="B22" s="12">
         <v>255</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="12">
         <v>0.313448</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <v>158.13</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>504.48500000000001</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="12">
         <v>25.04</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="14">
+      <c r="B23" s="12">
         <v>270</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="12">
         <v>8.9107699999999998E-2</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="12">
         <v>71.245599999999996</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>799.54399999999998</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>25.03</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="B24" s="12">
         <v>285</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="12">
         <v>2.4506300000000002E-2</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <v>31.053000000000001</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>1267.1400000000001</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="12">
         <v>25.01</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="14">
+      <c r="B25" s="12">
         <v>300</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13">
         <v>4.1812500000000001E-3</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <v>7.90123</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>1889.68</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="12">
         <v>24.99</v>
       </c>
     </row>
@@ -2112,36 +2122,36 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2496,376 +2506,376 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>15.000299999999999</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>789.59900000000005</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <v>251.245</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>0.318193</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>24.97</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>30.000299999999999</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>621.60199999999998</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>313.49900000000002</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>0.50434000000000001</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="12">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>45.000300000000003</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>467.31900000000002</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>373.55500000000001</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>0.79935699999999998</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>25.01</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <v>60.000300000000003</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>333.83300000000003</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>422.92599999999999</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>1.26688</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <v>25.04</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <v>75.000299999999996</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>216.90700000000001</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>435.47899999999998</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>2.0076800000000001</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>25.05</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <v>90.000299999999996</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>127.27800000000001</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <v>404.96499999999997</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>3.18174</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>25.06</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="14">
+      <c r="B10" s="12">
         <v>105</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <v>70.388000000000005</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <v>354.92</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>5.0423400000000003</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>25.06</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="14">
+      <c r="B11" s="12">
         <v>120</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="12">
         <v>43.227899999999998</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <v>345.44600000000003</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>7.9912799999999997</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <v>25.06</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <v>135</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="12">
         <v>26.796800000000001</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <v>339.375</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>12.6648</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>25.06</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <v>150</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <v>16.928999999999998</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <v>339.79599999999999</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>20.0718</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>25.05</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <v>165</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="12">
         <v>11.058299999999999</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="12">
         <v>351.77499999999998</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>31.8109</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>25.05</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="14">
+      <c r="B15" s="12">
         <v>180</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="12">
         <v>7.5275800000000004</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <v>379.53500000000003</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>50.419199999999996</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <v>25.04</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="14">
+      <c r="B16" s="12">
         <v>195</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="12">
         <v>5.0769099999999998</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="12">
         <v>405.67700000000002</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>79.906300000000002</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>25.03</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <v>210</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="12">
         <v>3.6134200000000001</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <v>457.64400000000001</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <v>126.651</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <v>25.03</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <v>225</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>2.76172</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>554.35699999999997</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>200.72900000000001</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>25.02</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="14">
+      <c r="B19" s="12">
         <v>240</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>1.83019</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <v>582.18200000000002</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>318.09899999999999</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>25.02</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="14">
+      <c r="B20" s="12">
         <v>255</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>0.88831899999999997</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <v>447.83100000000002</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>504.13299999999998</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>25.01</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="14">
+      <c r="B21" s="12">
         <v>270</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <v>0.33326</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <v>266.27100000000002</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>798.98800000000006</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>25.01</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="14">
+      <c r="B22" s="12">
         <v>285</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="12">
         <v>3.02171E-2</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <v>38.263800000000003</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>1266.3</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="12">
         <v>25.01</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="14">
+      <c r="B23" s="12">
         <v>300</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13">
         <v>3.8197999999999999E-3</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="12">
         <v>7.2133900000000004</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>1888.42</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>25</v>
       </c>
     </row>
@@ -2883,7 +2893,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD116DE-6982-41D5-A774-DFB13A230AE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{962CD438-C9C7-47B4-B743-CAAE2DF7CC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.aspentech.com/ProcessData/ExcelAddIn/IP21ConfigWorkBook"/>

--- a/data/up1_2_3_4_visc_sem.xlsx
+++ b/data/up1_2_3_4_visc_sem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arkema-my.sharepoint.com/personal/a6131250_arkema_com/Documents/finish_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942968FD-E942-4A03-B0F2-4A39AE5AC748}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D67CFA3D-15D0-42F4-B690-FEF0FC6E9158}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-15040" windowWidth="38620" windowHeight="21100" xr2:uid="{C900D49F-5873-4F17-88DC-CFF44F40CE34}"/>
+    <workbookView xWindow="-22890" yWindow="2490" windowWidth="21600" windowHeight="11190" xr2:uid="{C900D49F-5873-4F17-88DC-CFF44F40CE34}"/>
   </bookViews>
   <sheets>
     <sheet name="up1_2_3_4_psd" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>time</t>
   </si>
@@ -212,6 +212,15 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>up4_dry_air_scfm</t>
+  </si>
+  <si>
+    <t>up3_reject_solid%</t>
+  </si>
+  <si>
+    <t>up3_reject_lbhr</t>
   </si>
 </sst>
 </file>
@@ -655,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB923531-B7A6-45F3-88FD-ABB00CDC4AA5}">
-  <dimension ref="A3:AO18"/>
+  <dimension ref="A3:AP18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -675,14 +684,15 @@
     <col min="22" max="22" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.85546875" customWidth="1"/>
+    <col min="26" max="26" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -700,7 +710,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="J6" s="3"/>
       <c r="P6" s="4"/>
@@ -714,9 +724,10 @@
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
-      <c r="AG6" s="5"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="5"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -787,37 +798,46 @@
         <v>17</v>
       </c>
       <c r="Y12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB12" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AC12" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AD12" t="s">
         <v>3</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AE12" t="s">
         <v>4</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AF12" t="s">
         <v>5</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AG12" t="s">
         <v>6</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AH12" t="s">
         <v>7</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AI12" t="s">
         <v>8</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AJ12" t="s">
         <v>9</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AK12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44897.684027777781</v>
       </c>
@@ -892,38 +912,48 @@
       <c r="X13">
         <v>42.046659283415501</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13">
+        <v>1451.5554940010152</v>
+      </c>
+      <c r="Z13">
+        <f>0.00283721815010147*100</f>
+        <v>0.28372181501014704</v>
+      </c>
+      <c r="AA13">
+        <v>97.2</v>
+      </c>
+      <c r="AB13" s="3">
         <v>5.63</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AC13" s="3">
         <v>6.8</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AD13" s="3">
         <v>7.84</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AE13" s="3">
         <v>8.94</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AF13" s="3">
         <v>10.199999999999999</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AG13" s="3">
         <v>11.78</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AH13" s="3">
         <v>13.95</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AI13" s="3">
         <v>17.37</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AJ13" s="3">
         <v>24.51</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AK13" s="3">
         <v>60.36</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44902.488194444442</v>
       </c>
@@ -997,38 +1027,47 @@
       <c r="X14">
         <v>42.631066545074766</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14">
+        <v>1599.9867468979587</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB14" s="3">
         <v>5.47</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>6.43</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
         <v>7.21</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AE14" s="3">
         <v>7.95</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AF14" s="3">
         <v>8.7200000000000006</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AG14" s="3">
         <v>9.58</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AH14" s="3">
         <v>10.65</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AI14" s="3">
         <v>12.19</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AJ14" s="3">
         <v>15.04</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AK14" s="3">
         <v>29.54</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44902.617361111108</v>
       </c>
@@ -1102,38 +1141,47 @@
       <c r="X15">
         <v>42.446493159999214</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15">
+        <v>1598.9258127995515</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB15" s="3">
         <v>5.48</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>6.54</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
         <v>7.4</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AE15" s="3">
         <v>8.2100000000000009</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AF15" s="3">
         <v>9.07</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AG15" s="3">
         <v>10.039999999999999</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AH15" s="3">
         <v>11.24</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AI15" s="3">
         <v>12.95</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AJ15" s="3">
         <v>16.2</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AK15" s="3">
         <v>34.119999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44902.736111111109</v>
       </c>
@@ -1207,39 +1255,47 @@
       <c r="X16">
         <v>56.105365272337373</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="Y16">
+        <v>1702.2858345927227</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB16" s="3">
         <v>5.39</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AC16" s="3">
         <v>6.37</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AD16" s="3">
         <v>7.15</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AE16" s="3">
         <v>7.9</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AF16" s="3">
         <v>8.67</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AG16" s="3">
         <v>9.5299999999999994</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AH16" s="3">
         <v>10.59</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AI16" s="3">
         <v>12.11</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AJ16" s="3">
         <v>14.9</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AK16" s="3">
         <v>29.26</v>
       </c>
     </row>
-    <row r="17" spans="32:41" x14ac:dyDescent="0.25">
-      <c r="AF17" s="3"/>
+    <row r="17" spans="33:42" x14ac:dyDescent="0.25">
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
       <c r="AI17" s="3"/>
@@ -1249,9 +1305,9 @@
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
-    </row>
-    <row r="18" spans="32:41" x14ac:dyDescent="0.25">
-      <c r="AF18" s="3"/>
+      <c r="AP17" s="3"/>
+    </row>
+    <row r="18" spans="33:42" x14ac:dyDescent="0.25">
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
@@ -1261,6 +1317,7 @@
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2893,7 +2950,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{962CD438-C9C7-47B4-B743-CAAE2DF7CC5C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAC2636-C6D7-46EF-B4B8-BDC3B7EAD207}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.aspentech.com/ProcessData/ExcelAddIn/IP21ConfigWorkBook"/>

--- a/data/up1_2_3_4_visc_sem.xlsx
+++ b/data/up1_2_3_4_visc_sem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arkema-my.sharepoint.com/personal/a6131250_arkema_com/Documents/finish_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D67CFA3D-15D0-42F4-B690-FEF0FC6E9158}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{8CBE0929-3F08-4ACF-800D-7399D7C69A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8C523E-6DB0-4ECE-B4E2-621A3E26A545}"/>
   <bookViews>
-    <workbookView xWindow="-22890" yWindow="2490" windowWidth="21600" windowHeight="11190" xr2:uid="{C900D49F-5873-4F17-88DC-CFF44F40CE34}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{C900D49F-5873-4F17-88DC-CFF44F40CE34}"/>
   </bookViews>
   <sheets>
     <sheet name="up1_2_3_4_psd" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="62">
   <si>
     <t>time</t>
   </si>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>up3_reject_lbhr</t>
+  </si>
+  <si>
+    <t>up3_weir</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>up2_liq_out_lbhr</t>
   </si>
 </sst>
 </file>
@@ -664,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB923531-B7A6-45F3-88FD-ABB00CDC4AA5}">
-  <dimension ref="A3:AP18"/>
+  <dimension ref="A3:AQ18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -684,15 +693,15 @@
     <col min="22" max="22" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" customWidth="1"/>
-    <col min="26" max="26" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="22.85546875" customWidth="1"/>
+    <col min="27" max="27" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -710,7 +719,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="J6" s="3"/>
       <c r="P6" s="4"/>
@@ -725,9 +734,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
-      <c r="AH6" s="5"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="5"/>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -801,43 +811,49 @@
         <v>56</v>
       </c>
       <c r="Z12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA12" t="s">
         <v>57</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>58</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD12" t="s">
         <v>1</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AE12" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AF12" t="s">
         <v>3</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AG12" t="s">
         <v>4</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AH12" t="s">
         <v>5</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AI12" t="s">
         <v>6</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AJ12" t="s">
         <v>7</v>
       </c>
-      <c r="AI12" t="s">
+      <c r="AK12" t="s">
         <v>8</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AL12" t="s">
         <v>9</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AM12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44897.684027777781</v>
       </c>
@@ -913,47 +929,53 @@
         <v>42.046659283415501</v>
       </c>
       <c r="Y13">
-        <v>1451.5554940010152</v>
+        <v>1469.5634467351015</v>
       </c>
       <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
         <f>0.00283721815010147*100</f>
         <v>0.28372181501014704</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>97.2</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AC13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD13" s="3">
         <v>5.63</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AE13" s="3">
         <v>6.8</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AF13" s="3">
         <v>7.84</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AG13" s="3">
         <v>8.94</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AH13" s="3">
         <v>10.199999999999999</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AI13" s="3">
         <v>11.78</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AJ13" s="3">
         <v>13.95</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AK13" s="3">
         <v>17.37</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AL13" s="3">
         <v>24.51</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AM13" s="3">
         <v>60.36</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44902.488194444442</v>
       </c>
@@ -1028,46 +1050,52 @@
         <v>42.631066545074766</v>
       </c>
       <c r="Y14">
-        <v>1599.9867468979587</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>55</v>
+        <v>1427.6142482639557</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
       </c>
       <c r="AA14" t="s">
         <v>55</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD14" s="3">
         <v>5.47</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>6.43</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>7.21</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>7.95</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>8.7200000000000006</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>9.58</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>10.65</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>12.19</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>15.04</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>29.54</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44902.617361111108</v>
       </c>
@@ -1142,46 +1170,52 @@
         <v>42.446493159999214</v>
       </c>
       <c r="Y15">
-        <v>1598.9258127995515</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>55</v>
+        <v>1337.8548826947488</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
       </c>
       <c r="AA15" t="s">
         <v>55</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD15" s="3">
         <v>5.48</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>6.54</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>7.4</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>8.2100000000000009</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>9.07</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>10.039999999999999</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>11.24</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>12.95</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>16.2</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>34.119999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44902.736111111109</v>
       </c>
@@ -1256,47 +1290,52 @@
         <v>56.105365272337373</v>
       </c>
       <c r="Y16">
-        <v>1702.2858345927227</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>55</v>
+        <v>1262.0741875382669</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
       </c>
       <c r="AA16" t="s">
         <v>55</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AB16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD16" s="3">
         <v>5.39</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AE16" s="3">
         <v>6.37</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AF16" s="3">
         <v>7.15</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AG16" s="3">
         <v>7.9</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AH16" s="3">
         <v>8.67</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AI16" s="3">
         <v>9.5299999999999994</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AJ16" s="3">
         <v>10.59</v>
       </c>
-      <c r="AI16" s="3">
+      <c r="AK16" s="3">
         <v>12.11</v>
       </c>
-      <c r="AJ16" s="3">
+      <c r="AL16" s="3">
         <v>14.9</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AM16" s="3">
         <v>29.26</v>
       </c>
     </row>
-    <row r="17" spans="33:42" x14ac:dyDescent="0.25">
-      <c r="AG17" s="3"/>
+    <row r="17" spans="34:43" x14ac:dyDescent="0.25">
       <c r="AH17" s="3"/>
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
@@ -1306,9 +1345,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="33:42" x14ac:dyDescent="0.25">
-      <c r="AG18" s="3"/>
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="34:43" x14ac:dyDescent="0.25">
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
@@ -1318,6 +1357,7 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2950,7 +2990,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAC2636-C6D7-46EF-B4B8-BDC3B7EAD207}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4AAC02E-0B74-434B-A33E-E24EC3FAC122}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.aspentech.com/ProcessData/ExcelAddIn/IP21ConfigWorkBook"/>
